--- a/data/detallesBasedatosPruebaJuridica.xlsx
+++ b/data/detallesBasedatosPruebaJuridica.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col width="16.6640625" customWidth="1" min="1" max="1"/>
@@ -1609,6 +1609,120 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>784578</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>JUAN ALBERTO MURILLO DIAZ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1212121221001</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1212121221</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PLANILLA DE APORTES</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>123,25</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>456,25</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>593,00</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Dr. Christian Santiago Izurieta Cruz</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Mgs. Damian Patricio Pila Pila</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>DIRIGIDOS &amp; ASOCIADOS LTDA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>784577</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>JUAN ALBERTO MURILLO DIAZ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1212121221001</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1212121221</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PLANILLA DE APORTES</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>258,99</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>587,01</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>763,00</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Dr. Christian Santiago Izurieta Cruz</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Mgs. Damian Patricio Pila Pila</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>DIRIGIDOS &amp; ASOCIADOS LTDA.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
